--- a/data/processed/sectors.xlsx
+++ b/data/processed/sectors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,25 +758,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BAJAJAUTO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Diversified Financials</t>
+          <t>Two Wheelers</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -786,11 +786,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -800,11 +800,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Holding Companies</t>
+          <t>Diversified Financials</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.36</v>
+        <v>2.12</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -814,11 +814,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -828,11 +828,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Holding Companies</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.78</v>
+        <v>3.36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -842,11 +842,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -856,11 +856,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -870,25 +870,25 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Defence Electronics</t>
+          <t>Public Sector Banks</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -898,25 +898,25 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
+          <t>Defence Electronics</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.13</v>
+        <v>3.65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -926,25 +926,25 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -954,25 +954,25 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Auto Ancillaries</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.82</v>
+        <v>1.24</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -982,25 +982,25 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining</t>
+          <t>Auto Ancillaries</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Oil &amp; Gas Refining</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.66</v>
+        <v>2.57</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.96</v>
+        <v>0.66</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1080,11 +1080,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Public Sector Banks</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.94</v>
+        <v>2.96</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1094,25 +1094,25 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.95</v>
+        <v>3.94</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mining &amp; Metals</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.46</v>
+        <v>0.95</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1150,25 +1150,25 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Personal Products</t>
+          <t>Mining &amp; Metals</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1178,25 +1178,25 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Personal Products</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1234,25 +1234,25 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.07</v>
+        <v>2.86</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1262,81 +1262,81 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.01</v>
+        <v>3.07</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Two Wheelers</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.13</v>
+        <v>1.01</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gas Distribution</t>
+          <t>Two Wheelers</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1346,25 +1346,25 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Personal Products</t>
+          <t>Gas Distribution</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.89</v>
+        <v>3.12</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1374,39 +1374,39 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Diversified Industrials</t>
+          <t>Personal Products</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.61</v>
+        <v>0.89</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Defence &amp; Aerospace</t>
+          <t>Diversified Industrials</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.6</v>
+        <v>2.61</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Consumer Electricals</t>
+          <t>Defence &amp; Aerospace</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Consumer Electricals</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1486,25 +1486,25 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1514,11 +1514,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1528,11 +1528,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Private Banks</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1542,25 +1542,25 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Two Wheelers</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.26</v>
+        <v>0.93</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1570,25 +1570,25 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Two Wheelers</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1598,67 +1598,67 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.11</v>
+        <v>0.64</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3.87</v>
+        <v>1.11</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1668,11 +1668,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>General Insurance</t>
+          <t>Private Banks</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.51</v>
+        <v>3.87</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1682,11 +1682,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>General Insurance</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.47</v>
+        <v>3.51</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.03</v>
+        <v>2.47</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1738,25 +1738,25 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1766,25 +1766,25 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Private Banks</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.37</v>
+        <v>2.54</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1794,53 +1794,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Refining</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.27</v>
+        <v>3.37</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Travel &amp; Tourism</t>
+          <t>Oil &amp; Gas Refining</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3.97</v>
+        <v>0.27</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1850,53 +1850,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Speciality Finance</t>
+          <t>Travel &amp; Tourism</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.33</v>
+        <v>3.97</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>Speciality Finance</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.39</v>
+        <v>4.33</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1906,25 +1906,25 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Diversified FMCG</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1934,53 +1934,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Diversified Financials</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.38</v>
+        <v>1.41</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Diversified Financials</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.14</v>
+        <v>0.38</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1990,53 +1990,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.49</v>
+        <v>1.14</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Private Banks</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.47</v>
+        <v>4.49</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2046,11 +2046,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2060,11 +2060,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Private Banks</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.18</v>
+        <v>3.47</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2074,25 +2074,25 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2102,25 +2102,25 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.03</v>
+        <v>1.59</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.64</v>
+        <v>3.03</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2158,25 +2158,25 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2186,11 +2186,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.36</v>
+        <v>3.95</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2228,39 +2228,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Auto Ancillaries</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3.39</v>
+        <v>1.36</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Internet &amp; Platforms</t>
+          <t>Auto Ancillaries</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.44</v>
+        <v>3.39</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2270,25 +2270,25 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Internet &amp; Platforms</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2298,25 +2298,25 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2326,11 +2326,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.04</v>
+        <v>0.33</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2354,11 +2354,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2368,11 +2368,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Exploration</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.49</v>
+        <v>4.04</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Speciality Finance</t>
+          <t>Oil &amp; Gas Exploration</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.15</v>
+        <v>4.49</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Speciality Finance</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2438,25 +2438,25 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3.82</v>
+        <v>2.15</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2466,25 +2466,25 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Power Transmission</t>
+          <t>Public Sector Banks</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Speciality Finance</t>
+          <t>Power Transmission</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.78</v>
+        <v>4.12</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2522,25 +2522,25 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Conglomerates</t>
+          <t>Speciality Finance</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.24</v>
+        <v>1.78</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2550,25 +2550,25 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Conglomerates</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3.16</v>
+        <v>4.24</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2578,11 +2578,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2592,11 +2592,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Public Sector Banks</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2606,25 +2606,25 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Public Sector Banks</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Consumer Finance</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.15</v>
+        <v>2.86</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2662,25 +2662,25 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Finance</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2690,25 +2690,25 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.3</v>
+        <v>0.99</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2718,25 +2718,25 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Food &amp; Beverages</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Food &amp; Beverages</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.91</v>
+        <v>0.33</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2774,53 +2774,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Power &amp; Utilities</t>
+          <t>Automobiles</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.19</v>
+        <v>0.91</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power &amp; Utilities</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.01</v>
+        <v>4.19</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2830,39 +2830,39 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.39</v>
+        <v>1.1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2886,25 +2886,25 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Gems &amp; Jewellery</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2914,25 +2914,25 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Gems &amp; Jewellery</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.24</v>
+        <v>2.38</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2942,25 +2942,25 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.73</v>
+        <v>0.24</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2970,27 +2970,55 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Two Wheelers</t>
         </is>
       </c>
-      <c r="E92" t="n">
+      <c r="E93" t="n">
         <v>2.16</v>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
